--- a/ET-release8.1/Unity/Assets/Config/Excel/ItemConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/ItemConfig.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>Id</t>
   </si>
@@ -82,6 +82,14 @@
   </si>
   <si>
     <t>int</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>堆叠上限</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>StackingLimit</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -457,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C2:H14"/>
+  <dimension ref="C2:I14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -465,16 +473,17 @@
     <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
     <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
     <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="28.75" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="8" max="8" width="20.875" customWidth="1"/>
+    <col min="9" max="9" width="28.75" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="H2" s="2" t="s">
+    <row r="2" spans="3:9" x14ac:dyDescent="0.3">
+      <c r="I2" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="3:8" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:9" ht="14.25" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -491,10 +500,13 @@
         <v>17</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="3:8" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:9" ht="14.25" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -511,10 +523,13 @@
         <v>16</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="3:8" ht="14.25" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:9" ht="14.25" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>5</v>
       </c>
@@ -531,10 +546,13 @@
         <v>18</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="3:8" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
+    <row r="6" spans="3:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
@@ -550,9 +568,12 @@
       <c r="G6" s="1">
         <v>1</v>
       </c>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="3:8" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="H6" s="1">
+        <v>5</v>
+      </c>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" spans="3:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
@@ -568,9 +589,12 @@
       <c r="G7" s="1">
         <v>1</v>
       </c>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" spans="3:8" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="H7" s="1">
+        <v>10</v>
+      </c>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="8" spans="3:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
@@ -586,9 +610,12 @@
       <c r="G8" s="1">
         <v>1</v>
       </c>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="3:8" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
+      <c r="H8" s="1">
+        <v>5</v>
+      </c>
+      <c r="I8" s="4"/>
+    </row>
+    <row r="9" spans="3:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
@@ -604,33 +631,36 @@
       <c r="G9" s="1">
         <v>1</v>
       </c>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H9" s="1">
+        <v>10</v>
+      </c>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:9" x14ac:dyDescent="0.3">
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
